--- a/artfynd/A 20701-2023 artfynd.xlsx
+++ b/artfynd/A 20701-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20701-2023 artfynd.xlsx
+++ b/artfynd/A 20701-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>66539956</v>
       </c>
       <c r="B2" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548158.3634992511</v>
+        <v>548158</v>
       </c>
       <c r="R2" t="n">
-        <v>7265416.649956775</v>
+        <v>7265417</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,16 +780,11 @@
         <v>66539957</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548158.3634992511</v>
+        <v>548158</v>
       </c>
       <c r="R3" t="n">
-        <v>7265416.649956775</v>
+        <v>7265417</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +845,9 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66539953</v>
+        <v>66539958</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548151.6297533929</v>
+        <v>548084</v>
       </c>
       <c r="R4" t="n">
-        <v>7265723.317768722</v>
+        <v>7265319</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,21 +947,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,7 +963,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>22371</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1026,37 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66539954</v>
+        <v>66539953</v>
       </c>
       <c r="B5" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548151.6297533929</v>
+        <v>548152</v>
       </c>
       <c r="R5" t="n">
-        <v>7265723.317768722</v>
+        <v>7265723</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,21 +1049,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,7 +1065,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>22367</t>
+          <t>22366</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1143,37 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66539958</v>
+        <v>66539952</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548083.5051113338</v>
+        <v>548152</v>
       </c>
       <c r="R6" t="n">
-        <v>7265318.681666781</v>
+        <v>7265723</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1216,21 +1151,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1242,7 +1167,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>22371</t>
+          <t>22365</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1260,37 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66539952</v>
+        <v>66539954</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548151.6297533929</v>
+        <v>548152</v>
       </c>
       <c r="R7" t="n">
-        <v>7265723.317768722</v>
+        <v>7265723</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1333,21 +1253,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1359,7 +1269,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>22367</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
